--- a/research/traditional_assets/database/data/estonia/estonia_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_real_estate_operations_services.xlsx
@@ -594,64 +594,67 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>-15</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="J2">
-        <v>-15</v>
+        <v>0.2209302325581396</v>
       </c>
       <c r="K2">
-        <v>0.883</v>
+        <v>0.1</v>
       </c>
       <c r="L2">
-        <v>176.6</v>
+        <v>0.1661129568106312</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.966</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.2509090909090909</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>9.659999999999998</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>0.574</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.1490909090909091</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>5.739999999999999</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.392</v>
+      </c>
+      <c r="T2">
+        <v>0.4057971014492754</v>
       </c>
       <c r="U2">
-        <v>1.73</v>
+        <v>0.447</v>
       </c>
       <c r="V2">
-        <v>0.4240196078431372</v>
+        <v>0.1161038961038961</v>
       </c>
       <c r="W2">
-        <v>0.3532</v>
+        <v>0.02985074626865672</v>
       </c>
       <c r="X2">
-        <v>0.0445203742572353</v>
+        <v>0.07848416154219581</v>
       </c>
       <c r="Y2">
-        <v>0.3086796257427647</v>
+        <v>-0.04863341527353909</v>
       </c>
       <c r="Z2">
-        <v>0.002153316106804479</v>
+        <v>0.3716049382716049</v>
       </c>
       <c r="AA2">
-        <v>-0.03229974160206718</v>
+        <v>0.08209876543209876</v>
       </c>
       <c r="AB2">
-        <v>0.0445203742572353</v>
+        <v>0.07848416154219581</v>
       </c>
       <c r="AC2">
-        <v>-0.07682011585930248</v>
+        <v>0.003614603889902951</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-1.73</v>
+        <v>-0.447</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -672,10 +675,10 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.7361702127659574</v>
+        <v>-0.1313546870408463</v>
       </c>
       <c r="AK2">
-        <v>-1.067901234567901</v>
+        <v>-0.345707656612529</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -707,64 +710,67 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>-15</v>
+        <v>0.4418604651162791</v>
       </c>
       <c r="J3">
-        <v>-15</v>
+        <v>0.2209302325581396</v>
       </c>
       <c r="K3">
-        <v>0.883</v>
+        <v>0.1</v>
       </c>
       <c r="L3">
-        <v>176.6</v>
+        <v>0.1661129568106312</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.966</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.2509090909090909</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>9.659999999999998</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>0.574</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1490909090909091</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>5.739999999999999</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.392</v>
+      </c>
+      <c r="T3">
+        <v>0.4057971014492754</v>
       </c>
       <c r="U3">
-        <v>1.73</v>
+        <v>0.447</v>
       </c>
       <c r="V3">
-        <v>0.4240196078431372</v>
+        <v>0.1161038961038961</v>
       </c>
       <c r="W3">
-        <v>0.3532</v>
+        <v>0.02985074626865672</v>
       </c>
       <c r="X3">
-        <v>0.0445203742572353</v>
+        <v>0.07848416154219581</v>
       </c>
       <c r="Y3">
-        <v>0.3086796257427647</v>
+        <v>-0.04863341527353909</v>
       </c>
       <c r="Z3">
-        <v>0.002153316106804479</v>
+        <v>0.3716049382716049</v>
       </c>
       <c r="AA3">
-        <v>-0.03229974160206718</v>
+        <v>0.08209876543209876</v>
       </c>
       <c r="AB3">
-        <v>0.0445203742572353</v>
+        <v>0.07848416154219581</v>
       </c>
       <c r="AC3">
-        <v>-0.07682011585930248</v>
+        <v>0.003614603889902951</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -776,7 +782,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-1.73</v>
+        <v>-0.447</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -785,10 +791,10 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.7361702127659574</v>
+        <v>-0.1313546870408463</v>
       </c>
       <c r="AK3">
-        <v>-1.067901234567901</v>
+        <v>-0.345707656612529</v>
       </c>
       <c r="AL3">
         <v>0</v>

--- a/research/traditional_assets/database/data/estonia/estonia_real_estate_operations_services.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_real_estate_operations_services.xlsx
@@ -594,67 +594,67 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.4418604651162791</v>
+        <v>-1.655172413793103</v>
       </c>
       <c r="J2">
-        <v>0.2209302325581396</v>
+        <v>-1.655172413793103</v>
       </c>
       <c r="K2">
-        <v>0.1</v>
+        <v>-0.057</v>
       </c>
       <c r="L2">
-        <v>0.1661129568106312</v>
+        <v>-1.96551724137931</v>
       </c>
       <c r="M2">
-        <v>0.966</v>
+        <v>0.141</v>
       </c>
       <c r="N2">
-        <v>0.2509090909090909</v>
+        <v>0.04653465346534653</v>
       </c>
       <c r="O2">
-        <v>9.659999999999998</v>
+        <v>-2.473684210526315</v>
       </c>
       <c r="P2">
-        <v>0.574</v>
+        <v>0.141</v>
       </c>
       <c r="Q2">
-        <v>0.1490909090909091</v>
+        <v>0.04653465346534653</v>
       </c>
       <c r="R2">
-        <v>5.739999999999999</v>
+        <v>-2.473684210526315</v>
       </c>
       <c r="S2">
-        <v>0.392</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.4057971014492754</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>0.447</v>
+        <v>0.178</v>
       </c>
       <c r="V2">
-        <v>0.1161038961038961</v>
+        <v>0.05874587458745874</v>
       </c>
       <c r="W2">
-        <v>0.02985074626865672</v>
+        <v>-0.03275862068965518</v>
       </c>
       <c r="X2">
-        <v>0.07848416154219581</v>
+        <v>0.06991784598758138</v>
       </c>
       <c r="Y2">
-        <v>-0.04863341527353909</v>
+        <v>-0.1026764666772366</v>
       </c>
       <c r="Z2">
-        <v>0.3716049382716049</v>
+        <v>0.02242846094354215</v>
       </c>
       <c r="AA2">
-        <v>0.08209876543209876</v>
+        <v>-0.03712296983758701</v>
       </c>
       <c r="AB2">
-        <v>0.07848416154219581</v>
+        <v>0.06991784598758138</v>
       </c>
       <c r="AC2">
-        <v>0.003614603889902951</v>
+        <v>-0.1070408158251684</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.447</v>
+        <v>-0.178</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,16 +675,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.1313546870408463</v>
+        <v>-0.06241234221598878</v>
       </c>
       <c r="AK2">
-        <v>-0.345707656612529</v>
+        <v>-0.1084043848964677</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.001</v>
+      </c>
+      <c r="AQ2">
+        <v>48</v>
       </c>
     </row>
     <row r="3">
@@ -710,67 +713,67 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.4418604651162791</v>
+        <v>-1.655172413793103</v>
       </c>
       <c r="J3">
-        <v>0.2209302325581396</v>
+        <v>-1.655172413793103</v>
       </c>
       <c r="K3">
-        <v>0.1</v>
+        <v>-0.057</v>
       </c>
       <c r="L3">
-        <v>0.1661129568106312</v>
+        <v>-1.96551724137931</v>
       </c>
       <c r="M3">
-        <v>0.966</v>
+        <v>0.141</v>
       </c>
       <c r="N3">
-        <v>0.2509090909090909</v>
+        <v>0.04653465346534653</v>
       </c>
       <c r="O3">
-        <v>9.659999999999998</v>
+        <v>-2.473684210526315</v>
       </c>
       <c r="P3">
-        <v>0.574</v>
+        <v>0.141</v>
       </c>
       <c r="Q3">
-        <v>0.1490909090909091</v>
+        <v>0.04653465346534653</v>
       </c>
       <c r="R3">
-        <v>5.739999999999999</v>
+        <v>-2.473684210526315</v>
       </c>
       <c r="S3">
-        <v>0.392</v>
+        <v>0</v>
       </c>
       <c r="T3">
-        <v>0.4057971014492754</v>
+        <v>0</v>
       </c>
       <c r="U3">
-        <v>0.447</v>
+        <v>0.178</v>
       </c>
       <c r="V3">
-        <v>0.1161038961038961</v>
+        <v>0.05874587458745874</v>
       </c>
       <c r="W3">
-        <v>0.02985074626865672</v>
+        <v>-0.03275862068965518</v>
       </c>
       <c r="X3">
-        <v>0.07848416154219581</v>
+        <v>0.06991784598758138</v>
       </c>
       <c r="Y3">
-        <v>-0.04863341527353909</v>
+        <v>-0.1026764666772366</v>
       </c>
       <c r="Z3">
-        <v>0.3716049382716049</v>
+        <v>0.02242846094354215</v>
       </c>
       <c r="AA3">
-        <v>0.08209876543209876</v>
+        <v>-0.03712296983758701</v>
       </c>
       <c r="AB3">
-        <v>0.07848416154219581</v>
+        <v>0.06991784598758138</v>
       </c>
       <c r="AC3">
-        <v>0.003614603889902951</v>
+        <v>-0.1070408158251684</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -782,7 +785,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.447</v>
+        <v>-0.178</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -791,16 +794,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.1313546870408463</v>
+        <v>-0.06241234221598878</v>
       </c>
       <c r="AK3">
-        <v>-0.345707656612529</v>
+        <v>-0.1084043848964677</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.001</v>
+      </c>
+      <c r="AQ3">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
